--- a/AAII_Financials/Quarterly/REPYY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/REPYY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="92">
   <si>
     <t>REPYY</t>
   </si>
@@ -656,173 +656,177 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -862,86 +866,89 @@
       <c r="O8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P8" s="3">
+      <c r="P8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q8" s="3">
         <v>17643000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>22579100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>22846800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>18807400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>16794900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14390600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>11451800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>10275400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>8509800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>8393500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>6661100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>11919900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>14269300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>14910600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>15069700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>14501500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>15497200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>15703000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>14765000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12094500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12700900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11270400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11424100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>11880100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>11748700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10471600</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,86 +988,89 @@
       <c r="O9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q9" s="3">
         <v>13357700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>17878000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>16261700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>13988900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12911600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>11193300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>8432300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>7333400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6419300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6240900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4988700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>10154000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>10917600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>11619000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>11461700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>11033700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>12563600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>11959100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>10741900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>8909200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9153200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>7993100</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8607900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>8323500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>7909100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>7400900</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1100,86 +1110,89 @@
       <c r="O10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P10" s="3">
+      <c r="P10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q10" s="3">
         <v>4285300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>4701000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>6585200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>4818500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>3883200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>3197300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>3019500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2941900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2090600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2152600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1672400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1765900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>3351600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>3291500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3608000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3467800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>2933600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3743900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>4023000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3185300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3547700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3277300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>2816200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3556600</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3839500</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3070700</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,86 +1520,89 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>932600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>32400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1715900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>189900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>612500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>47400</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>44400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-15300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1510100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>650200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>6800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>6343700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-12200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>-162300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>35900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>971200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>17700</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>538200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>91100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>226600</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>2200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>-210900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>50500</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>56300</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>-494200</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1619,86 +1642,89 @@
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="3">
+      <c r="P15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q15" s="3">
         <v>681200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>660300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>590800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>618500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>558300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>546000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>505700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>514500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>532600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>547000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>617500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>654900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>806700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>731300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>700000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>659100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>661200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>676600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>582000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>567700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>486900</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>646300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>886400</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>703100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>907400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>701900</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,8 +1763,9 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1778,86 +1805,89 @@
       <c r="O17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P17" s="3">
+      <c r="P17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="3">
         <v>16770200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>20980700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21000300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>16697100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>15626200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>13326600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10685800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>9260700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>9422400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8276200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>7963600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>12485600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>20674800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>14180500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>14055600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>13563700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>15779900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>14614700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>14030400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11236900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>11714700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>10540000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10959600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>10889400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>11171100</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>9602900</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1897,86 +1927,89 @@
       <c r="O18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P18" s="3">
+      <c r="P18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="3">
         <v>872800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1598400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1846500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>2110300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1168700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1064000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>766000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>1014700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-912600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>117300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-1302500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-565700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-6405600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>730100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>1014100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>937800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-282700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1088300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>734600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>857500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>986200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>730400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>464500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>990700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>577500</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>868600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,86 +2093,89 @@
       <c r="O20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q20" s="3">
         <v>613600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>44300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>489600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>245200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>75900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>196000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>256000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>52100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>454800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-150500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1150900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-71100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-49000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>39200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>68200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>604500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>141900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>647000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>79100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>386000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>55000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-38100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>23500</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3500</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-61000</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2178,86 +2215,89 @@
       <c r="O21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="3">
+      <c r="P21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q21" s="3">
         <v>2167600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2303000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2927000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>2974000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1802900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1806000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1527800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1581200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>74800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>513800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-1838200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>20300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-5647900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1500600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1710500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1665100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>983000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1906800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1963600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1504300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1859100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1431700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1312700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1717300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1479000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>1511900</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2303,8 +2343,8 @@
       <c r="Q22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -2375,8 +2415,11 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2416,86 +2459,89 @@
       <c r="O23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P23" s="3">
+      <c r="P23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q23" s="3">
         <v>1486400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1642700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>2336200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>2355500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1244500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1260000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1022000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1066700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-457800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-33200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-2453500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-636800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6454600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>769300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>1010500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>1006000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>321700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1230200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>1381600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>936600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1372200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>785400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>426400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1014200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>574000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>807600</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2535,86 +2581,89 @@
       <c r="O24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P24" s="3">
+      <c r="P24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q24" s="3">
         <v>299100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>901300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>1059800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>821300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>623400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>494300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>396800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>400200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>248400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>65400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-271600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-53100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-297700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>352800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>389400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>267900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>132500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>480300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>664800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>336000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>887500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>227800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>67300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>194900</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>186600</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>232400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,8 +2781,11 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2773,86 +2825,89 @@
       <c r="O26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P26" s="3">
+      <c r="P26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q26" s="3">
         <v>1187300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>741400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1276300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1534200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>621200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>765700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>625300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>666600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-706200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-98600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-2181800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-583700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-6156900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>416500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>621100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>738100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>189300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>750000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>716800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>600600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>484700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>557600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>359000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>819300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>387400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>575200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2892,86 +2947,89 @@
       <c r="O27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P27" s="3">
+      <c r="P27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q27" s="3">
         <v>1123100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>721900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1231700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1494000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>593000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>744100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>600900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>646200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-723100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-113100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-2198200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-557800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6174400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>399300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>609400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>718900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>192800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>731000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>692000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>587400</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>466700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>529600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>345600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>800500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>363900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3130,8 +3191,8 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -3185,31 +3246,34 @@
         <v>0</v>
       </c>
       <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="3">
         <v>406900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>74700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>129000</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>53900</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>57200</v>
       </c>
-      <c r="AM29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AN29" s="3">
+      <c r="AN29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AO29" s="3">
         <v>351000</v>
       </c>
-      <c r="AO29" s="3" t="s">
+      <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,86 +3557,89 @@
       <c r="O32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-613600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-44300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-489600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-245200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-75900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-196000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-256000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-52100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-454800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>150500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1150900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>71100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>49000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-39200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-68200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-604500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-141900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-647000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-79100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-386000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-55000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>38100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-23500</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3500</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>61000</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3606,86 +3679,89 @@
       <c r="O33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P33" s="3">
+      <c r="P33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="3">
         <v>1123100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>721900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1231700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1494000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>593000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>744100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>600900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>646200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-723100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-113100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-2198200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-557800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6174400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>399300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>609400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>718900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>192800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>731000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>1098900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>662100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>595800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>583400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>402800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>800500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>714900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,8 +3879,11 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3844,210 +3923,216 @@
       <c r="O35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P35" s="3">
+      <c r="P35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q35" s="3">
         <v>1123100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>721900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1231700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1494000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>593000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>744100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>600900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>646200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-723100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-113100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-2198200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-557800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6174400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>399300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>609400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>718900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>192800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>731000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>1098900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>662100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>595800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>583400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>402800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>800500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>714900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,1079 +4218,1107 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3435400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3828800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5011100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4121000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3534400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>4926000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>4375400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3823000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3743700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4563900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>4479300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5732500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5964800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7212700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8160400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2612500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5374000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2718900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6015600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2201700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4286300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4309800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5157300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2630200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3572500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2766800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3369900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3536300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4047900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4878300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4075100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>4867600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3447700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4210800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4976000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>4707900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>3505000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3764400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2652800</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5929400</v>
+      </c>
+      <c r="E42" s="3">
         <v>5687400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4354100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>3734600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>3545200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>2358400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>3583500</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>4070500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5057700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5242600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>3962700</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>4150700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>3787500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>3938600</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3666800</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>5316500</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>2521500</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>6003700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>2163500</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>4792700</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1519000</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1579900</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>837600</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>4616700</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2947000</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>4175800</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>4558200</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3713900</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>3112500</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>3092100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4239500</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3934300</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>1120000</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>1307100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>1776100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>2053200</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>2553000</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>3314800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>2914600</v>
       </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8830100</v>
+      </c>
+      <c r="E43" s="3">
         <v>7550800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7102000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7974200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8050200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7451100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7518400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>8428200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7700900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8535400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>8662200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>8330800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>8412600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9446700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>11121500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>12879800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>10464800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8930800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>7598600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>5534400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>4434400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>4045500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>4092400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>4244700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>5032400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>6704400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>6956700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>7652500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7406900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>6936500</v>
-      </c>
-      <c r="AG43" s="3">
-        <v>7350500</v>
       </c>
       <c r="AH43" s="3">
         <v>7350500</v>
       </c>
       <c r="AI43" s="3">
+        <v>7350500</v>
+      </c>
+      <c r="AJ43" s="3">
         <v>5817200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>6565900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>6948500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>6438000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>6217700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>6832700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>5626100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9137400</v>
+      </c>
+      <c r="E44" s="3">
         <v>6428300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>6645500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>6027000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>6612600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>6430300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6571500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7551700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>8215600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>7320700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7676800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6744500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>8372400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>8077700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>8344100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>9813600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>7976900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5666600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5639700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4883700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4396600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>3370200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>3555800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>3541100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>4287200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5366600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5233200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>5619700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5191500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5192900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5726400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5582100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>4773000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4260200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4026800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>3611700</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4407700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4231600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>3987400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1450900</v>
+      </c>
+      <c r="E45" s="3">
         <v>1599200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>346100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4398100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>3152800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>848900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>373600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>570000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>460700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>265300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1053100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>317700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>321600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>324500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>476600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>553800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>461100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1009300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1124300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1182800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>392000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>243400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>423500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>805100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>223600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>233500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>251100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>241200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>265600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>357200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>428200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>275600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3861700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>228900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>279400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>389300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>483600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>552900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>882700</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>28783300</v>
+      </c>
+      <c r="E46" s="3">
         <v>25094500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>23458900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>26254800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>24895200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22014700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>22422500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>24443400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>25178600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>25927900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>25834000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>25276200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>26859000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>29000300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>31769300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>31176200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>26798400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>24329400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>22541700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>18595400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>15028200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>13548700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>14066700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>15837800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>16062600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>19247100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20369100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>20763500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>20024400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>20457100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>21819800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>22010200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>19019600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>16572900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>18006800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>17200100</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17167000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>18696400</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>16063600</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>6293800</v>
+      </c>
+      <c r="E47" s="3">
         <v>5658100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>6082400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>5136800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4600100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4934300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4523800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4649100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4772900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5104500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4354400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4520700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4449200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>6437400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>6122200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>6054200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>5716900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>5206900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>5119600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4744100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7489600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6795300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7186400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7958200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>9161500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>9772400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>11049400</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>10022900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>10278900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>9853600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>9543600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>9340200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>8446900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>12687500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>11871800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>12058000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>13548100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>13358000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>12867300</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>28281700</v>
+      </c>
+      <c r="E48" s="3">
         <v>30118600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>30058700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>29500900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28780800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28964700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>30907900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>29824300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>29036600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28060100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25872100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25980300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25253200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>24887800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>24765300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>24062200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>24058800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>23553200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>22519100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21883700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>21662400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20872600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>23182500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>25130200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>26449200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>27096800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>34049800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>31932200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>32653900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>30162800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>30003100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>29858800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>26738500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27676100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27832100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>28554600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>31491000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>32119000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>31446400</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3163500</v>
+      </c>
+      <c r="E49" s="3">
         <v>3428400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3495200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3465600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3316000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3235300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3512200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3386900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3334800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2737900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2503200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2917000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2831400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2188600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3038900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3413400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3477400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3791100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3615200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3505200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3548300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3344300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4019800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4310200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>4833700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5218300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>6786400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>6158500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>6091100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>6028100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>5760700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>5636500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>5014600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>5143200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>5203800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>5350800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>5999300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>5997000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>5923000</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,127 +5558,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1463500</v>
+      </c>
+      <c r="E52" s="3">
         <v>1033200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1602700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1235500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1614800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1205100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1526900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1367200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1431700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>829000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3309700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3235800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3083400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3902100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4275200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4255600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4037300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4104400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4922500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4708100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4646700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4613000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4833500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5228700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>6383900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>6252600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>5782000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>5210300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>5516900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>5392800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>4788400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>5014300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>4673100</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>5079200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>5225100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>5249800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>5865500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5950000</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>5859700</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>71564000</v>
+      </c>
+      <c r="E54" s="3">
         <v>69775700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>68441900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>69360000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>66570500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>65416700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>67294200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>67852800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>68102300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>68125300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>64614700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>64802400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>65315100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>66416100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>69971000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>68961600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>64088800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>60985000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>58718000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>53436400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>52375200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>49173800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>53288900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>58465100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>62890900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>67587200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>78036800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>74087300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>74565100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>71894300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>71915600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>71860000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>63892600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>67159000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>68139600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>68413300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>74070900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>76120400</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>72160000</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,722 +6014,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11751400</v>
+      </c>
+      <c r="E57" s="3">
         <v>5455000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>11464300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>9810900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>11201900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5667300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>10340200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>10072900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>10342000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5411700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11772900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11637600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11084300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>5577900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>14421900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>17284500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13692700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>12166900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11084500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>8735900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>7583500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5883700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5985600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5443600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>6435900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>8335300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>7972200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>9317100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8511000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3837300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>3728500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3610200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2720800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3072000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>2957600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>2294500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>2183300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>2497900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>1957900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2279200</v>
+      </c>
+      <c r="E58" s="3">
         <v>2163900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3373200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4164400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3671600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2878100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3472000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3446900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>2625200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2542300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2385400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>3347500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>3927500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5750400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4661400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>4780500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>4998800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>5344700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>5443400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4113800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>3869900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>4273000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>5737100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7662100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7521600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7498200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>6924300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5545600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4443000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3917800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>4818000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>5413100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>4645000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>4755000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>4507000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>4885400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4577900</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>4560300</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4375600</v>
+      </c>
+      <c r="E59" s="3">
         <v>7869000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1155700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7317700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4258500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7022500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1331700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3991200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6019000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7828000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2243900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>2527300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2190400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9233000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1577800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1782300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1520100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1608800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1337500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1370100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>975900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>738100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>798100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1332000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1039900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1753400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1199300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1298700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1009600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6872600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6455100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6282400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5432900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>5786100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8402600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8407100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>9159200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>10222700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>9028900</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>18406300</v>
+      </c>
+      <c r="E60" s="3">
         <v>16296800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15993200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>21293000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>19132100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16236700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15143900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>17511000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16361000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16826600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16559100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>16550200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>16622100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18738400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>21750200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>23728200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>19993300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>18774400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>17766700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>15549400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>12673200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>10491700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>11056700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>12512700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>15137800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17610400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>16669700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>17540100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>15066100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>15152900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>14101400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>14710500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>13566900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>13503100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>16115100</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>15208600</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>16227900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>17298400</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>15547100</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>12327200</v>
+      </c>
+      <c r="E61" s="3">
         <v>13388500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>14011500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>10004700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>9413100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>9737000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11128700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>9911100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>9759400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>9229600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10605400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10909400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>9952200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11220000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10095900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>9898400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>11151600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11041600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10518100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>8876600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>12032200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>109700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>12882400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>13698600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>12542000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>12560200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>14197600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>12439300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>14081700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>9411200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>9276300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>9184000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>8428200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>9798300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>10427800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>11184000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>11583200</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>12848500</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>12833300</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4790400</v>
+      </c>
+      <c r="E62" s="3">
         <v>4823300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4348200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4246600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4217500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>6564900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5984800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6258400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6069700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6285000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3965900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4084100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4926100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>7690100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>8202500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>7756000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6531700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>6458000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>7008500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6832600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6435100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>18086900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6468200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7228400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7493800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7987400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>8459800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7725400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>8122200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>10762000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>11249400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>11108600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>9743700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>10127100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>7874100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>8155700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>9372900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>9455000</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>9525500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>38597100</v>
+      </c>
+      <c r="E66" s="3">
         <v>37348800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>37171200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>38411000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>35569600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35290400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35741700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>37096300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>35600400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>35993100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>33529800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>34127700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>34070000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>38400500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>40796400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41846100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>38144300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>36685900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>35576500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>31528400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>31396700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>28931600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>30661600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>33710200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>35458300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>38486000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>39671300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>38024800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>37593000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>35664400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>34981900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>35346200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>32038500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>33731500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>34715500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>34829900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>37479800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>39888400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>38178200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>22200400</v>
+      </c>
+      <c r="E72" s="3">
         <v>2489100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1381000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>20901900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>395600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2031300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1998700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>20412500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1045400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>20575900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2947700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>19307900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1208200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>4708400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3482000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>17477100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1510300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2709200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2088100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>14545400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>661500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-3280400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2675700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>17304000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-549900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19422200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>28052300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>26559600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>26621400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>25795500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>27093100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>26343200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>23588300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>23824300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>23432800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>22843700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>23736800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>22936200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>22436200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30032000</v>
+      </c>
+      <c r="E76" s="3">
         <v>29517400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>28298700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27984700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>28276000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>27424200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>28580200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>27956700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>29340800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>28956600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>28333000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>27884300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>28593000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>28015600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>29174600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>27115500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>25944500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>24299000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>23141500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>21908000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20978500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20242200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>22627300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>24754900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>27432600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>29101200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>38365500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>36062500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>36972100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>36229900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>36933700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>36513800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>31854100</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>33427400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>33424100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>33583400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>36591200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>36232000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>33981800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,132 +8496,138 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8472,86 +8667,89 @@
       <c r="O81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P81" s="3">
+      <c r="P81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q81" s="3">
         <v>1123100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>721900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1231700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1494000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>593000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>744100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>600900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>646200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-723100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-113100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-2198200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-557800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6174400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>399300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>609400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>718900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>192800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>731000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>1098900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>662100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>595800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>583400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>402800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>800500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>714900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>556400</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>692800</v>
+      </c>
+      <c r="E83" s="3">
         <v>692600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>807500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>654700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>729300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>567000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>604400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>556800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>626900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>418900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>599100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>567600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>633200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>681200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>660300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>590800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>618500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>558300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>546000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>505700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>514500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>532600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>547000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>615300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>657100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>806700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>731300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>700000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>659100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>661200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>676600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>582000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>567700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>486900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>646300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>886400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>703100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>905000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>704300</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2210700</v>
+      </c>
+      <c r="E89" s="3">
         <v>1775300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1486600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1834400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1106800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1664800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1448800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>876500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1337800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2366500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1181200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1796900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1747100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>2687000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3322100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1770300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>764900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2020800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1370900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>767100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>832000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1001400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1159300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>330500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>354500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>2033600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1512900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1307000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>910300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2081900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>1715200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>697900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>855300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2070100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1330700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>1574200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>797000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1934400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>752400</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-963100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1203500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-1046600</v>
       </c>
-      <c r="F91" s="3">
-        <v>-1190800</v>
-      </c>
       <c r="G91" s="3">
+        <v>-1432800</v>
+      </c>
+      <c r="H91" s="3">
         <v>-880900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1351100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1366300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1475400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1293600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1502200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1110300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1109200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-939800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1457000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-869000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-633000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-576000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-828000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-426000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-350200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-323600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-580500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-373600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-446200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-604100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1630900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-853800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-807000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-534700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1103600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-729800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-684900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-584100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-1019900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-570000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-536300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-475400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-732500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-443700</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-998500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-2604200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1851500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-611900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1573700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>295100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-658000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-462900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2111300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1330800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1270100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1494500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2259900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2724700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-276700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-626700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-879900</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1403900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-746300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-767100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-224600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1139000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>257400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>619600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>618700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1760500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2246600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1145800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-108900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2446200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-811500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>2310200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-612700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-996300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-878500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-648500</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-633900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-531700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>1861700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,127 +10221,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E96" s="3">
         <v>37600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>666400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>32900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>615000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>33100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>655800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>30000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>544800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>35400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>472100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>30600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>513900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-45400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-516600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-54400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-496900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-34700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-481400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-29600</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-120500</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-18000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-207600</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>12000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-156900</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>14000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-253600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>15300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-256000</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-119500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-215200</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-212100</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-5600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-162000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-5900</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-169000</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1351500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-372200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1382100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-871400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1062500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1138800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-319000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-304300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>31300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1112000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1023500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-574200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-601900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-979100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>321000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1846500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-594600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-676500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>126000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>762800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-758500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-520600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1743700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1401800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-788100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-1105500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-35500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-372900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1191400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-236600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1398200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-794900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-1073800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-1040100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-591300</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>219900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-1294700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>98600</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-1245400</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-78900</v>
+      </c>
+      <c r="E101" s="3">
         <v>43500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-75800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>31300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-37600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>33900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>10900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-129300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>102000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>26100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-134000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>112400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>27200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>69400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-26900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>26500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>12000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-38200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>23700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>35500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>15600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>31900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-22000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-19100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-29200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>24700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-4700</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-133700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1185900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>894100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>280700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1608300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>864500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>395900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>105000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-711000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-113800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1078500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-260900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1110400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1150800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>3478800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-675700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-696600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>9800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>723700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>756500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-124500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-646300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-328000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>2313800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>208900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-845200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-733800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-201200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-374400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-609200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-498000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2245100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-853100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>14600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-144700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>1116400</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1132700</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1526000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1364000</v>
       </c>
     </row>
